--- a/TM, RR4/get_data.xlsx
+++ b/TM, RR4/get_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ngt_VKHL\TM, RR4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutymanager.vkhl\Documents\ngt_VKHL\TM, RR4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DC80A0-1DD3-4C7A-8112-FEA1D8FBC749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0738A2DA-CF02-4312-9017-0877D2CA9F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="6240" windowWidth="20010" windowHeight="13815" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="780" windowWidth="16320" windowHeight="12600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,89 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="355">
+  <si>
+    <t>LN</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>Dubrovin</t>
+  </si>
+  <si>
+    <t>Roni</t>
+  </si>
+  <si>
+    <t>05-04-2011</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>40109442</t>
+  </si>
+  <si>
+    <t>Guy</t>
+  </si>
+  <si>
+    <t>24-04-2012</t>
+  </si>
+  <si>
+    <t>40090126</t>
+  </si>
+  <si>
+    <t>Tongrit</t>
+  </si>
+  <si>
+    <t>Pattraporn</t>
+  </si>
+  <si>
+    <t>Oron</t>
+  </si>
+  <si>
+    <t>Hen Michael</t>
+  </si>
+  <si>
+    <t>Zim</t>
+  </si>
+  <si>
+    <t>Lilah</t>
+  </si>
+  <si>
+    <t>Naiyana</t>
+  </si>
+  <si>
+    <t>Urai</t>
+  </si>
+  <si>
+    <t>Kazak</t>
+  </si>
+  <si>
+    <t>Jantasan</t>
+  </si>
+  <si>
+    <t>Thaweesak</t>
+  </si>
+  <si>
+    <t>24-10-1994</t>
+  </si>
+  <si>
+    <t>11912225858</t>
+  </si>
   <si>
     <t>ชื่อ
 First Name *</t>
@@ -69,12 +142,6 @@
 Phone No.</t>
   </si>
   <si>
-    <t>Lilah</t>
-  </si>
-  <si>
-    <t>Zim</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -123,12 +190,6 @@
     <t>21/10/2016</t>
   </si>
   <si>
-    <t>Hen Michael</t>
-  </si>
-  <si>
-    <t>Oron</t>
-  </si>
-  <si>
     <t>102003004</t>
   </si>
   <si>
@@ -165,12 +226,6 @@
     <t>13/11/2012</t>
   </si>
   <si>
-    <t>Urai</t>
-  </si>
-  <si>
-    <t>Naiyana</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -210,12 +265,6 @@
     <t>02/08/1966</t>
   </si>
   <si>
-    <t>Pattraporn</t>
-  </si>
-  <si>
-    <t>Tongrit</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
@@ -225,25 +274,10 @@
     <t>24/11/1976</t>
   </si>
   <si>
-    <t>Guy</t>
-  </si>
-  <si>
-    <t>Dubrovin</t>
-  </si>
-  <si>
-    <t>40090126</t>
-  </si>
-  <si>
     <t>24/04/2012</t>
   </si>
   <si>
     <t>07/07/2026</t>
-  </si>
-  <si>
-    <t>Roni</t>
-  </si>
-  <si>
-    <t>40109442</t>
   </si>
   <si>
     <t>05/04/2011</t>
@@ -963,9 +997,6 @@
     <t>146</t>
   </si>
   <si>
-    <t>Israel</t>
-  </si>
-  <si>
     <t>Phuket</t>
   </si>
   <si>
@@ -1078,33 +1109,6 @@
   </si>
   <si>
     <t>3306</t>
-  </si>
-  <si>
-    <t>LN</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>BD</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>PN</t>
-  </si>
-  <si>
-    <t>05-04-2011</t>
-  </si>
-  <si>
-    <t>24-04-2012</t>
-  </si>
-  <si>
-    <t>Kazak</t>
-  </si>
-  <si>
-    <t>SSTTE</t>
   </si>
 </sst>
 </file>
@@ -2621,1681 +2625,1681 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="79.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
         <v>85</v>
       </c>
-      <c r="F20" t="s">
-        <v>72</v>
-      </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H30" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="H31" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F32" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G35" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G36" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H36" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="H37" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H39" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F40" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H40" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F41" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G41" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H41" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F42" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G42" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H42" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" t="s">
         <v>164</v>
       </c>
-      <c r="F43" t="s">
-        <v>151</v>
-      </c>
       <c r="G43" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H43" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" t="s">
+        <v>164</v>
+      </c>
+      <c r="G44" t="s">
+        <v>178</v>
+      </c>
+      <c r="H44" t="s">
         <v>166</v>
-      </c>
-      <c r="C44" t="s">
-        <v>149</v>
-      </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" t="s">
-        <v>151</v>
-      </c>
-      <c r="G44" t="s">
-        <v>165</v>
-      </c>
-      <c r="H44" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H45" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C46" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F46" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H46" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H47" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C48" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F48" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G48" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="H48" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E49" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G49" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="H50" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H51" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E52" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G52" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H52" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G53" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E54" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G54" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G55" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D57" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E57" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G57" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="H57" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F58" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G58" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="H58" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F59" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G59" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H59" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C60" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F60" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G60" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H60" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="C61" t="s">
         <v>217</v>
       </c>
-      <c r="C61" t="s">
-        <v>204</v>
-      </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F61" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G61" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E62" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="F62" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="G62" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="H62" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E63" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="F63" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="G63" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="H63" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F64" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G64" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H64" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E65" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F65" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G65" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="H65" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C66" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E66" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="G66" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="H66" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F67" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="G67" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="H67" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C68" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F68" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="G68" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H68" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C69" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
+        <v>263</v>
+      </c>
+      <c r="F69" t="s">
         <v>250</v>
       </c>
-      <c r="F69" t="s">
-        <v>237</v>
-      </c>
       <c r="G69" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="H69" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" t="s">
+        <v>266</v>
+      </c>
+      <c r="F70" t="s">
+        <v>250</v>
+      </c>
+      <c r="G70" t="s">
+        <v>267</v>
+      </c>
+      <c r="H70" t="s">
         <v>252</v>
-      </c>
-      <c r="C70" t="s">
-        <v>249</v>
-      </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" t="s">
-        <v>253</v>
-      </c>
-      <c r="F70" t="s">
-        <v>237</v>
-      </c>
-      <c r="G70" t="s">
-        <v>254</v>
-      </c>
-      <c r="H70" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D71" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G71" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="H71" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="D72" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E72" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G72" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="H72" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E73" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G73" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="H73" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4339,13 +4343,13 @@
     <col min="25" max="25" width="18.85546875" style="5" customWidth="1"/>
     <col min="26" max="26" width="15.28515625" style="5" customWidth="1"/>
     <col min="27" max="27" width="12.28515625" style="5" customWidth="1"/>
-    <col min="28" max="38" width="9.140625" style="5" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="28" max="39" width="9.140625" style="5" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="8" customFormat="1" ht="91.5" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -4358,23 +4362,23 @@
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
       <c r="L1" s="15" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="M1" s="16"/>
       <c r="N1" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
       <c r="R1" s="9"/>
       <c r="Z1" s="17" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="AA1" s="16"/>
     </row>
     <row r="2" spans="1:29" s="8" customFormat="1" ht="29.25" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -4387,11 +4391,11 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="15" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="M2" s="16"/>
       <c r="N2" s="10" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
@@ -4399,85 +4403,85 @@
     </row>
     <row r="3" spans="1:29" s="8" customFormat="1" ht="51" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AA3" s="12" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
@@ -4487,58 +4491,58 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M4">
         <v>60</v>
       </c>
       <c r="O4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S4" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T4" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>60</v>
       </c>
       <c r="V4" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X4" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y4" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z4" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="15" customHeight="1">
@@ -4546,58 +4550,58 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I5" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M5">
         <v>60</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R5" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S5" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T5" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>60</v>
       </c>
       <c r="V5" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W5" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X5" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="15" customHeight="1">
@@ -4605,58 +4609,58 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C6" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M6">
         <v>60</v>
       </c>
       <c r="O6" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="Q6" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R6" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S6" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T6" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>60</v>
       </c>
       <c r="V6" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W6" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X6" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y6" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z6" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="15" customHeight="1">
@@ -4664,58 +4668,58 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I7" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="Q7" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R7" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S7" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T7" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>60</v>
       </c>
       <c r="V7" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W7" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X7" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y7" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z7" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="15" customHeight="1">
@@ -4723,58 +4727,58 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="O8" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q8" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R8" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S8" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T8" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>60</v>
       </c>
       <c r="V8" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W8" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X8" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y8" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z8" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="15" customHeight="1">
@@ -4782,58 +4786,58 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I9" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="M9">
         <v>60</v>
       </c>
       <c r="O9" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R9" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S9" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T9" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>60</v>
       </c>
       <c r="V9" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W9" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y9" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z9" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="15" customHeight="1">
@@ -4841,58 +4845,58 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D10" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I10" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M10">
         <v>60</v>
       </c>
       <c r="O10" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="Q10" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R10" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S10" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T10" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>60</v>
       </c>
       <c r="V10" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W10" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X10" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y10" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z10" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="15" customHeight="1">
@@ -4900,58 +4904,58 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I11" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="L11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M11">
         <v>60</v>
       </c>
       <c r="O11" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="Q11" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R11" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S11" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T11" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>60</v>
       </c>
       <c r="V11" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W11" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X11" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y11" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z11" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1">
@@ -4959,58 +4963,58 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="I12" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="M12">
         <v>60</v>
       </c>
       <c r="O12" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R12" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S12" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T12" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="U12">
         <v>99</v>
       </c>
       <c r="V12" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W12" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X12" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="Y12" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z12" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="15" customHeight="1">
@@ -5018,58 +5022,58 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D13" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="I13" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="M13">
         <v>16</v>
       </c>
       <c r="O13" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="Q13" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R13" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S13" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T13" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="U13">
         <v>16</v>
       </c>
       <c r="V13" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W13" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X13" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="Y13" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z13" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="15" customHeight="1">
@@ -5077,58 +5081,58 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C14" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="I14" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M14">
         <v>16</v>
       </c>
       <c r="O14" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="Q14" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R14" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S14" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T14" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="U14">
         <v>16</v>
       </c>
       <c r="V14" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W14" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X14" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="Y14" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z14" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="15" customHeight="1">
@@ -5136,58 +5140,58 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D15" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="I15" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>60</v>
       </c>
       <c r="O15" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R15" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S15" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T15" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>60</v>
       </c>
       <c r="V15" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W15" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X15" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y15" t="s">
         <v>319</v>
       </c>
-      <c r="Y15" t="s">
-        <v>307</v>
-      </c>
       <c r="Z15" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="15" customHeight="1">
@@ -5195,58 +5199,58 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D16" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="I16" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>60</v>
       </c>
       <c r="O16" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R16" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S16" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T16" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>60</v>
       </c>
       <c r="V16" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W16" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X16" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y16" t="s">
         <v>319</v>
       </c>
-      <c r="Y16" t="s">
-        <v>307</v>
-      </c>
       <c r="Z16" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1">
@@ -5254,58 +5258,58 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C17" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D17" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M17">
         <v>79</v>
       </c>
       <c r="O17" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R17" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S17" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T17" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U17">
         <v>79</v>
       </c>
       <c r="V17" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W17" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X17" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y17" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z17" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1">
@@ -5313,58 +5317,58 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D18" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="I18" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J18" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M18">
         <v>79</v>
       </c>
       <c r="O18" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="Q18" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R18" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S18" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T18" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U18">
         <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W18" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X18" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y18" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z18" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1">
@@ -5372,58 +5376,58 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C19" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D19" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="I19" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M19">
         <v>79</v>
       </c>
       <c r="O19" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="Q19" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R19" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S19" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T19" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U19">
         <v>79</v>
       </c>
       <c r="V19" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W19" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X19" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y19" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z19" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1">
@@ -5431,58 +5435,58 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C20" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D20" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="I20" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J20" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L20" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M20">
         <v>79</v>
       </c>
       <c r="O20" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="Q20" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R20" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S20" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T20" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U20">
         <v>79</v>
       </c>
       <c r="V20" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W20" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X20" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y20" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z20" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1">
@@ -5490,58 +5494,58 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C21" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D21" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="I21" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L21" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M21">
         <v>79</v>
       </c>
       <c r="O21" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="Q21" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R21" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S21" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T21" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U21">
         <v>79</v>
       </c>
       <c r="V21" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W21" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X21" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y21" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z21" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1">
@@ -5549,58 +5553,58 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D22" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="I22" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J22" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="M22">
         <v>79</v>
       </c>
       <c r="O22" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="Q22" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R22" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S22" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T22" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U22">
         <v>79</v>
       </c>
       <c r="V22" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W22" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X22" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y22" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z22" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1">
@@ -5608,58 +5612,58 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C23" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D23" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="I23" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J23" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="M23">
         <v>79</v>
       </c>
       <c r="O23" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="Q23" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R23" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S23" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T23" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U23">
         <v>79</v>
       </c>
       <c r="V23" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W23" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X23" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y23" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z23" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1">
@@ -5667,58 +5671,58 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C24" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D24" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="I24" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J24" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="M24">
         <v>79</v>
       </c>
       <c r="O24" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="Q24" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R24" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S24" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T24" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U24">
         <v>79</v>
       </c>
       <c r="V24" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W24" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X24" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y24" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z24" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1">
@@ -5726,58 +5730,58 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D25" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="I25" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J25" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="L25" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="M25">
         <v>79</v>
       </c>
       <c r="O25" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="Q25" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R25" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S25" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T25" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U25">
         <v>79</v>
       </c>
       <c r="V25" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W25" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X25" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y25" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z25" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1">
@@ -5785,58 +5789,58 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C26" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D26" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="I26" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M26">
         <v>79</v>
       </c>
       <c r="O26" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="Q26" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R26" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S26" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T26" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U26">
         <v>79</v>
       </c>
       <c r="V26" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W26" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X26" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y26" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z26" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1">
@@ -5844,58 +5848,58 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C27" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D27" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="I27" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J27" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L27" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M27">
         <v>79</v>
       </c>
       <c r="O27" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="Q27" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R27" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S27" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T27" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U27">
         <v>79</v>
       </c>
       <c r="V27" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W27" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X27" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y27" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z27" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1">
@@ -5903,58 +5907,58 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C28" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D28" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="I28" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J28" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="L28" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M28">
         <v>79</v>
       </c>
       <c r="O28" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="Q28" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R28" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S28" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T28" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U28">
         <v>79</v>
       </c>
       <c r="V28" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W28" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X28" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y28" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z28" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1">
@@ -5962,58 +5966,58 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C29" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D29" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="I29" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J29" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="L29" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M29">
         <v>79</v>
       </c>
       <c r="O29" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="Q29" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R29" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S29" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T29" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U29">
         <v>79</v>
       </c>
       <c r="V29" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W29" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X29" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y29" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z29" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1">
@@ -6021,58 +6025,58 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C30" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D30" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="I30" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L30" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M30">
         <v>79</v>
       </c>
       <c r="O30" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="Q30" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R30" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S30" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T30" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U30">
         <v>79</v>
       </c>
       <c r="V30" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W30" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X30" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y30" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z30" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15" customHeight="1">
@@ -6080,58 +6084,58 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C31" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D31" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="I31" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J31" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="L31" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M31">
         <v>79</v>
       </c>
       <c r="O31" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="Q31" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R31" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S31" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T31" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U31">
         <v>79</v>
       </c>
       <c r="V31" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W31" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X31" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="Y31" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z31" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="15" customHeight="1">
@@ -6139,58 +6143,58 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C32" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D32" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="I32" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J32" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M32">
         <v>79</v>
       </c>
       <c r="O32" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="Q32" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R32" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S32" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T32" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U32">
         <v>79</v>
       </c>
       <c r="V32" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W32" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X32" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="Y32" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z32" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15" customHeight="1">
@@ -6198,58 +6202,58 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C33" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D33" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="I33" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="L33" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M33">
         <v>79</v>
       </c>
       <c r="O33" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="Q33" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R33" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S33" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T33" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U33">
         <v>79</v>
       </c>
       <c r="V33" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W33" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X33" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="Y33" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z33" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="15" customHeight="1">
@@ -6257,58 +6261,58 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C34" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D34" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="I34" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J34" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M34">
         <v>79</v>
       </c>
       <c r="O34" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="Q34" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R34" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S34" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T34" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U34">
         <v>79</v>
       </c>
       <c r="V34" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W34" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X34" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="Y34" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z34" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="15" customHeight="1">
@@ -6316,58 +6320,58 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C35" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D35" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I35" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J35" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="M35">
         <v>60</v>
       </c>
       <c r="O35" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="Q35" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R35" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S35" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T35" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>60</v>
       </c>
       <c r="V35" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W35" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X35" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y35" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z35" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="15" customHeight="1">
@@ -6375,58 +6379,58 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D36" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I36" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J36" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="L36" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="M36">
         <v>60</v>
       </c>
       <c r="O36" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="Q36" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R36" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S36" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T36" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>60</v>
       </c>
       <c r="V36" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W36" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X36" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y36" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z36" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="15" customHeight="1">
@@ -6434,58 +6438,58 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C37" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D37" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I37" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="M37">
         <v>60</v>
       </c>
       <c r="O37" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="Q37" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R37" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S37" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T37" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>60</v>
       </c>
       <c r="V37" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W37" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X37" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y37" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z37" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="15" customHeight="1">
@@ -6493,58 +6497,58 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C38" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D38" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I38" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J38" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="M38">
         <v>60</v>
       </c>
       <c r="O38" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="Q38" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R38" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S38" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T38" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>60</v>
       </c>
       <c r="V38" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W38" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X38" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y38" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z38" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="15" customHeight="1">
@@ -6552,58 +6556,58 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C39" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D39" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I39" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J39" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="L39" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="M39">
         <v>60</v>
       </c>
       <c r="O39" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="Q39" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R39" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S39" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T39" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>60</v>
       </c>
       <c r="V39" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W39" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X39" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Y39" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z39" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1">
@@ -6611,58 +6615,58 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C40" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D40" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I40" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J40" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="L40" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M40">
         <v>126</v>
       </c>
       <c r="O40" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="Q40" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R40" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S40" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T40" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U40">
         <v>126</v>
       </c>
       <c r="V40" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W40" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X40" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y40" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z40" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:26" ht="15" customHeight="1">
@@ -6670,58 +6674,58 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C41" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D41" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I41" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J41" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="L41" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M41">
         <v>126</v>
       </c>
       <c r="O41" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="Q41" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R41" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S41" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T41" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U41">
         <v>126</v>
       </c>
       <c r="V41" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W41" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X41" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y41" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z41" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="15" customHeight="1">
@@ -6729,58 +6733,58 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C42" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D42" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I42" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J42" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M42">
         <v>126</v>
       </c>
       <c r="O42" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="Q42" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R42" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S42" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T42" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U42">
         <v>126</v>
       </c>
       <c r="V42" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W42" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X42" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y42" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z42" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="15" customHeight="1">
@@ -6788,58 +6792,58 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C43" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D43" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I43" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J43" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M43">
         <v>126</v>
       </c>
       <c r="O43" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="Q43" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R43" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S43" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T43" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U43">
         <v>126</v>
       </c>
       <c r="V43" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W43" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X43" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y43" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z43" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:26" ht="15" customHeight="1">
@@ -6847,58 +6851,58 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C44" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D44" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I44" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J44" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M44">
         <v>126</v>
       </c>
       <c r="O44" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="Q44" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R44" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S44" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T44" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U44">
         <v>126</v>
       </c>
       <c r="V44" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W44" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X44" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y44" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z44" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="15" customHeight="1">
@@ -6906,58 +6910,58 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C45" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D45" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="I45" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J45" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="M45">
         <v>126</v>
       </c>
       <c r="O45" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="Q45" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R45" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S45" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T45" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="U45">
         <v>126</v>
       </c>
       <c r="V45" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W45" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X45" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y45" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z45" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="15" customHeight="1">
@@ -6965,58 +6969,58 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C46" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D46" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="I46" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J46" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="L46" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M46">
         <v>79</v>
       </c>
       <c r="O46" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Q46" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R46" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S46" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T46" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U46">
         <v>79</v>
       </c>
       <c r="V46" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W46" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X46" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y46" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z46" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="15" customHeight="1">
@@ -7024,58 +7028,58 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C47" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="I47" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L47" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M47">
         <v>79</v>
       </c>
       <c r="O47" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="Q47" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R47" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S47" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T47" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U47">
         <v>79</v>
       </c>
       <c r="V47" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W47" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X47" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y47" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z47" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="15" customHeight="1">
@@ -7083,58 +7087,58 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C48" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D48" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="I48" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J48" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M48">
         <v>79</v>
       </c>
       <c r="O48" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="Q48" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R48" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S48" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T48" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U48">
         <v>79</v>
       </c>
       <c r="V48" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W48" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X48" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y48" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z48" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="15" customHeight="1">
@@ -7142,58 +7146,58 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D49" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="I49" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J49" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="L49" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M49">
         <v>79</v>
       </c>
       <c r="O49" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="Q49" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R49" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S49" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T49" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="U49">
         <v>79</v>
       </c>
       <c r="V49" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W49" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X49" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Y49" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z49" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="15" customHeight="1">
@@ -7201,58 +7205,58 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C50" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D50" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I50" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J50" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M50">
         <v>60</v>
       </c>
       <c r="O50" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="Q50" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R50" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S50" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T50" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U50">
         <v>60</v>
       </c>
       <c r="V50" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W50" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X50" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y50" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z50" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="15" customHeight="1">
@@ -7260,58 +7264,58 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D51" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I51" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J51" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="L51" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M51">
         <v>60</v>
       </c>
       <c r="O51" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="Q51" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R51" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S51" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T51" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U51">
         <v>60</v>
       </c>
       <c r="V51" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W51" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X51" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y51" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z51" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="15" customHeight="1">
@@ -7319,58 +7323,58 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C52" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I52" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J52" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="L52" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M52">
         <v>60</v>
       </c>
       <c r="O52" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="Q52" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R52" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S52" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T52" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U52">
         <v>60</v>
       </c>
       <c r="V52" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W52" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X52" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y52" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z52" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="15" customHeight="1">
@@ -7378,58 +7382,58 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C53" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D53" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I53" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J53" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="L53" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M53">
         <v>60</v>
       </c>
       <c r="O53" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="Q53" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R53" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S53" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T53" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U53">
         <v>60</v>
       </c>
       <c r="V53" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W53" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X53" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y53" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z53" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="15" customHeight="1">
@@ -7437,58 +7441,58 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C54" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D54" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I54" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J54" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="M54">
         <v>60</v>
       </c>
       <c r="O54" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="Q54" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R54" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S54" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T54" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U54">
         <v>60</v>
       </c>
       <c r="V54" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W54" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X54" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y54" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z54" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="15" customHeight="1">
@@ -7496,58 +7500,58 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C55" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D55" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="I55" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J55" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="L55" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M55">
         <v>60</v>
       </c>
       <c r="O55" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="Q55" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R55" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S55" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T55" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U55">
         <v>60</v>
       </c>
       <c r="V55" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W55" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X55" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y55" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z55" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="15" customHeight="1">
@@ -7555,58 +7559,58 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C56" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D56" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="I56" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J56" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M56">
         <v>60</v>
       </c>
       <c r="O56" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="Q56" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R56" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S56" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T56" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U56">
         <v>60</v>
       </c>
       <c r="V56" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W56" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X56" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y56" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z56" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="15" customHeight="1">
@@ -7614,58 +7618,58 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D57" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="I57" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J57" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="L57" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M57">
         <v>60</v>
       </c>
       <c r="O57" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="Q57" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R57" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S57" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T57" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U57">
         <v>60</v>
       </c>
       <c r="V57" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W57" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X57" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Y57" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z57" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="15" customHeight="1">
@@ -7673,58 +7677,58 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C58" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D58" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I58" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J58" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="L58" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="M58">
         <v>12</v>
       </c>
       <c r="O58" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="Q58" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R58" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S58" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T58" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="U58">
         <v>126</v>
       </c>
       <c r="V58" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W58" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X58" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y58" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z58" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="15" customHeight="1">
@@ -7732,58 +7736,58 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C59" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D59" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I59" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J59" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="L59" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="M59">
         <v>12</v>
       </c>
       <c r="O59" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="Q59" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R59" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S59" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T59" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="U59">
         <v>126</v>
       </c>
       <c r="V59" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W59" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X59" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y59" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z59" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="15" customHeight="1">
@@ -7791,58 +7795,58 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C60" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D60" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I60" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J60" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="M60">
         <v>12</v>
       </c>
       <c r="O60" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="Q60" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R60" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S60" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T60" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="U60">
         <v>126</v>
       </c>
       <c r="V60" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W60" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X60" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y60" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z60" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="15" customHeight="1">
@@ -7850,58 +7854,58 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C61" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D61" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I61" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J61" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="M61">
         <v>12</v>
       </c>
       <c r="O61" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="Q61" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R61" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S61" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T61" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="U61">
         <v>126</v>
       </c>
       <c r="V61" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W61" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X61" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y61" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z61" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="15" customHeight="1">
@@ -7909,58 +7913,58 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D62" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I62" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J62" t="s">
+        <v>230</v>
+      </c>
+      <c r="L62" t="s">
         <v>217</v>
-      </c>
-      <c r="L62" t="s">
-        <v>204</v>
       </c>
       <c r="M62">
         <v>12</v>
       </c>
       <c r="O62" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="Q62" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R62" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S62" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T62" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="U62">
         <v>126</v>
       </c>
       <c r="V62" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W62" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X62" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Y62" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z62" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="15" customHeight="1">
@@ -7968,58 +7972,58 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C63" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D63" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="I63" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J63" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="L63" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="M63">
         <v>220</v>
       </c>
       <c r="O63" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="Q63" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R63" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S63" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T63" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="U63">
         <v>220</v>
       </c>
       <c r="V63" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W63" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X63" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y63" t="s">
         <v>319</v>
       </c>
-      <c r="Y63" t="s">
-        <v>307</v>
-      </c>
       <c r="Z63" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="15" customHeight="1">
@@ -8027,58 +8031,58 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D64" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="I64" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J64" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="L64" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="M64">
         <v>220</v>
       </c>
       <c r="O64" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="Q64" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R64" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S64" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T64" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="U64">
         <v>220</v>
       </c>
       <c r="V64" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W64" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X64" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y64" t="s">
         <v>319</v>
       </c>
-      <c r="Y64" t="s">
-        <v>307</v>
-      </c>
       <c r="Z64" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="15" customHeight="1">
@@ -8086,58 +8090,58 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C65" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D65" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="I65" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J65" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="L65" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M65">
         <v>16</v>
       </c>
       <c r="O65" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="Q65" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R65" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S65" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T65" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="U65">
         <v>16</v>
       </c>
       <c r="V65" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W65" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X65" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="Y65" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z65" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1">
@@ -8145,58 +8149,58 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C66" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D66" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="I66" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J66" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="L66" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="M66">
         <v>16</v>
       </c>
       <c r="O66" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="Q66" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R66" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S66" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T66" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="U66">
         <v>16</v>
       </c>
       <c r="V66" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W66" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X66" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="Y66" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z66" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="15" customHeight="1">
@@ -8204,58 +8208,58 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C67" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I67" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J67" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="M67">
         <v>17</v>
       </c>
       <c r="O67" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="Q67" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R67" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S67" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T67" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U67">
         <v>17</v>
       </c>
       <c r="V67" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W67" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X67" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Y67" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z67" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="15" customHeight="1">
@@ -8263,58 +8267,58 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C68" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D68" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I68" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J68" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="L68" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="M68">
         <v>17</v>
       </c>
       <c r="O68" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="Q68" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R68" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S68" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T68" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U68">
         <v>17</v>
       </c>
       <c r="V68" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W68" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X68" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Y68" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z68" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:26" ht="15" customHeight="1">
@@ -8322,58 +8326,58 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D69" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I69" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J69" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="L69" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="M69">
         <v>17</v>
       </c>
       <c r="O69" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="Q69" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R69" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S69" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T69" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U69">
         <v>17</v>
       </c>
       <c r="V69" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W69" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X69" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Y69" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z69" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" spans="1:26" ht="15" customHeight="1">
@@ -8381,58 +8385,58 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D70" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I70" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J70" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="L70" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="M70">
         <v>17</v>
       </c>
       <c r="O70" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="Q70" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R70" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S70" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T70" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U70">
         <v>17</v>
       </c>
       <c r="V70" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W70" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X70" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Y70" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z70" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="1:26" ht="15" customHeight="1">
@@ -8440,58 +8444,58 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C71" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I71" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J71" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="L71" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="M71">
         <v>17</v>
       </c>
       <c r="O71" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="Q71" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R71" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S71" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T71" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U71">
         <v>17</v>
       </c>
       <c r="V71" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W71" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X71" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Y71" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z71" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72" spans="1:26" ht="15" customHeight="1">
@@ -8499,58 +8503,58 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C72" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D72" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="I72" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J72" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="L72" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="M72">
         <v>60</v>
       </c>
       <c r="O72" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="Q72" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R72" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S72" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T72" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U72">
         <v>60</v>
       </c>
       <c r="V72" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W72" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X72" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y72" t="s">
         <v>319</v>
       </c>
-      <c r="Y72" t="s">
-        <v>307</v>
-      </c>
       <c r="Z72" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:26" ht="15" customHeight="1">
@@ -8558,58 +8562,58 @@
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C73" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D73" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="I73" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J73" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="L73" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="M73">
         <v>60</v>
       </c>
       <c r="O73" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="Q73" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R73" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S73" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T73" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U73">
         <v>60</v>
       </c>
       <c r="V73" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W73" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X73" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y73" t="s">
         <v>319</v>
       </c>
-      <c r="Y73" t="s">
-        <v>307</v>
-      </c>
       <c r="Z73" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="15" customHeight="1">
@@ -8617,58 +8621,58 @@
         <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C74" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="I74" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="J74" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="M74">
         <v>60</v>
       </c>
       <c r="O74" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="Q74" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="R74" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="S74" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="T74" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="U74">
         <v>60</v>
       </c>
       <c r="V74" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="W74" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="X74" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y74" t="s">
         <v>319</v>
       </c>
-      <c r="Y74" t="s">
-        <v>307</v>
-      </c>
       <c r="Z74" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -8692,7 +8696,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
@@ -8700,61 +8704,61 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>344</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>345</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>346</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>347</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>35012000</v>
@@ -8762,13 +8766,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>102003004</v>
@@ -8776,10 +8780,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>100002</v>
@@ -8787,13 +8791,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>11</v>
@@ -8801,11 +8805,28 @@
     </row>
     <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>350</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>